--- a/artfynd/A 16463-2025 artfynd.xlsx
+++ b/artfynd/A 16463-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105927511</v>
+        <v>105927101</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>gammalett  granskog, Ås lm</t>
+          <t>V myren, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543028.0183279773</v>
+        <v>543010</v>
       </c>
       <c r="R2" t="n">
-        <v>7245804.810755167</v>
+        <v>7245892</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +746,14 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>spår på två granar.</t>
+          <t>på murken moss- och lavbevuxen granlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105927101</v>
+        <v>105927511</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +792,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>V myren, Ås lm</t>
+          <t>gammalett  granskog, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543009.9943604189</v>
+        <v>543028</v>
       </c>
       <c r="R3" t="n">
-        <v>7245892.724271171</v>
+        <v>7245805</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,24 +853,14 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på murken moss- och lavbevuxen granlåga.</t>
+          <t>spår på två granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +869,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -914,127 +884,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>105927112</v>
-      </c>
-      <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>gammalett  granskog, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>543028.0183279773</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7245804.810755167</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ett par fruktkroppar på stående gran</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Gry Benediktson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Gry Benediktson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
